--- a/Hand_edited_log/1/student/dungdvhe181404/TC1/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/dungdvhe181404/TC1/GradeDetail.xlsx
@@ -1044,10 +1044,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1100,10 +1100,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1156,10 +1156,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
         <x:v>52</x:v>
@@ -1212,10 +1212,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>52</x:v>
@@ -1268,10 +1268,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1324,10 +1324,10 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1380,10 +1380,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>52</x:v>
@@ -1436,10 +1436,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1492,10 +1492,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>52</x:v>
@@ -1548,10 +1548,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
         <x:v>52</x:v>
@@ -1604,10 +1604,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="0">
-        <x:v>4002</x:v>
+        <x:v>4001</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>49680</x:v>
+        <x:v>50167</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>52</x:v>
